--- a/artfynd/A 59265-2022 artfynd.xlsx
+++ b/artfynd/A 59265-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120348418</v>
+        <v>120348254</v>
       </c>
       <c r="B2" t="n">
-        <v>105588</v>
+        <v>108811</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,20 +687,20 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220785</v>
+        <v>220299</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120348254</v>
+        <v>120346664</v>
       </c>
       <c r="B3" t="n">
-        <v>108811</v>
+        <v>100194</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -799,25 +799,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220299</v>
+        <v>222498</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -831,10 +831,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>608493</v>
+        <v>608438</v>
       </c>
       <c r="R3" t="n">
-        <v>6557369</v>
+        <v>6557282</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -899,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120346664</v>
+        <v>120348418</v>
       </c>
       <c r="B4" t="n">
-        <v>100194</v>
+        <v>105588</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -911,25 +911,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>222498</v>
+        <v>220785</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -943,10 +943,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>608438</v>
+        <v>608493</v>
       </c>
       <c r="R4" t="n">
-        <v>6557282</v>
+        <v>6557369</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>

--- a/artfynd/A 59265-2022 artfynd.xlsx
+++ b/artfynd/A 59265-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120348254</v>
+        <v>120346664</v>
       </c>
       <c r="B2" t="n">
-        <v>108811</v>
+        <v>100194</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220299</v>
+        <v>222498</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -719,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>608493</v>
+        <v>608438</v>
       </c>
       <c r="R2" t="n">
-        <v>6557369</v>
+        <v>6557282</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120346664</v>
+        <v>120348418</v>
       </c>
       <c r="B3" t="n">
-        <v>100194</v>
+        <v>105588</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -799,25 +799,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>222498</v>
+        <v>220785</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -831,10 +831,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>608438</v>
+        <v>608493</v>
       </c>
       <c r="R3" t="n">
-        <v>6557282</v>
+        <v>6557369</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -899,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120348418</v>
+        <v>120348254</v>
       </c>
       <c r="B4" t="n">
-        <v>105588</v>
+        <v>108811</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -911,20 +911,20 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220785</v>
+        <v>220299</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">

--- a/artfynd/A 59265-2022 artfynd.xlsx
+++ b/artfynd/A 59265-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120346664</v>
+        <v>120348254</v>
       </c>
       <c r="B2" t="n">
-        <v>100194</v>
+        <v>108811</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>222498</v>
+        <v>220299</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -719,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>608438</v>
+        <v>608493</v>
       </c>
       <c r="R2" t="n">
-        <v>6557282</v>
+        <v>6557369</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -899,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120348254</v>
+        <v>120346664</v>
       </c>
       <c r="B4" t="n">
-        <v>108811</v>
+        <v>100194</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -911,25 +911,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220299</v>
+        <v>222498</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -943,10 +943,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>608493</v>
+        <v>608438</v>
       </c>
       <c r="R4" t="n">
-        <v>6557369</v>
+        <v>6557282</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>

--- a/artfynd/A 59265-2022 artfynd.xlsx
+++ b/artfynd/A 59265-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120348254</v>
+        <v>120346664</v>
       </c>
       <c r="B2" t="n">
-        <v>108811</v>
+        <v>100194</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220299</v>
+        <v>222498</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -719,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>608493</v>
+        <v>608438</v>
       </c>
       <c r="R2" t="n">
-        <v>6557369</v>
+        <v>6557282</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -899,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120346664</v>
+        <v>120348254</v>
       </c>
       <c r="B4" t="n">
-        <v>100194</v>
+        <v>108811</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -911,25 +911,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>222498</v>
+        <v>220299</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -943,10 +943,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>608438</v>
+        <v>608493</v>
       </c>
       <c r="R4" t="n">
-        <v>6557282</v>
+        <v>6557369</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
